--- a/ui_runner/templates/graded_analysis_tabs_2026-06-24.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-24.xlsx
@@ -471,13 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55.9</v>
       </c>
     </row>
     <row r="3">
@@ -497,13 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>61.5</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>181</v>
+      </c>
+      <c r="G4" t="n">
+        <v>50.5</v>
       </c>
     </row>
     <row r="5">
@@ -549,13 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -601,13 +613,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48.8</v>
       </c>
     </row>
     <row r="8">
@@ -627,13 +642,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>172</v>
+      </c>
+      <c r="G8" t="n">
+        <v>47.9</v>
       </c>
     </row>
     <row r="9">
@@ -653,13 +671,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55.4</v>
       </c>
     </row>
     <row r="10">
@@ -679,13 +700,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -705,13 +729,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1391</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>835</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>556</v>
+      </c>
+      <c r="G11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -731,13 +758,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="G12" t="n">
+        <v>69.8</v>
       </c>
     </row>
     <row r="13">
@@ -757,13 +787,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>122</v>
+      </c>
+      <c r="G13" t="n">
+        <v>47.6</v>
       </c>
     </row>
     <row r="14">
@@ -783,13 +816,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>314</v>
+      </c>
+      <c r="G14" t="n">
+        <v>27.5</v>
       </c>
     </row>
     <row r="15">
@@ -809,13 +845,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>544</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>430</v>
+      </c>
+      <c r="G15" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -835,13 +874,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>246</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19.1</v>
       </c>
     </row>
     <row r="17">
@@ -861,13 +903,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>5178</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>926</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4252</v>
+      </c>
+      <c r="G17" t="n">
+        <v>17.9</v>
       </c>
     </row>
   </sheetData>
@@ -1057,26 +1102,47 @@
           <t>Elite</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>56.2</v>
+      </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48.7</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="H2" t="n">
+        <v>66.7</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>25</v>
       </c>
       <c r="M2" t="n">
+        <v>16</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1090,11 +1156,17 @@
       <c r="W2" t="n">
         <v>0</v>
       </c>
+      <c r="X2" t="n">
+        <v>41.5</v>
+      </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>100</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1102,8 +1174,11 @@
       <c r="AE2" t="n">
         <v>0</v>
       </c>
+      <c r="AF2" t="n">
+        <v>82.40000000000001</v>
+      </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -1112,26 +1187,47 @@
           <t>Above Avg</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>75</v>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="D3" t="n">
+        <v>63</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="F3" t="n">
+        <v>63.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>28.6</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28.6</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>36.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>50</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1145,11 +1241,17 @@
       <c r="W3" t="n">
         <v>0</v>
       </c>
+      <c r="X3" t="n">
+        <v>50</v>
+      </c>
       <c r="Y3" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1157,8 +1259,11 @@
       <c r="AE3" t="n">
         <v>0</v>
       </c>
+      <c r="AF3" t="n">
+        <v>44.7</v>
+      </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -1167,26 +1272,47 @@
           <t>Avg</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>79.5</v>
+      </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="D4" t="n">
+        <v>59.1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="F4" t="n">
+        <v>69.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>33.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>100</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1200,8 +1326,11 @@
       <c r="W4" t="n">
         <v>0</v>
       </c>
+      <c r="X4" t="n">
+        <v>61.5</v>
+      </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1212,8 +1341,11 @@
       <c r="AE4" t="n">
         <v>0</v>
       </c>
+      <c r="AF4" t="n">
+        <v>39.4</v>
+      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -1222,23 +1354,41 @@
           <t>Below Avg</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>90.5</v>
+      </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>92.3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1255,8 +1405,11 @@
       <c r="W5" t="n">
         <v>0</v>
       </c>
+      <c r="X5" t="n">
+        <v>58.3</v>
+      </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1267,8 +1420,11 @@
       <c r="AE5" t="n">
         <v>0</v>
       </c>
+      <c r="AF5" t="n">
+        <v>51.9</v>
+      </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -1277,26 +1433,47 @@
           <t>Weak</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>80.8</v>
+      </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="D6" t="n">
+        <v>85.7</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>62.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>60</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>66.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>66.7</v>
       </c>
       <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1310,20 +1487,29 @@
       <c r="W6" t="n">
         <v>0</v>
       </c>
+      <c r="X6" t="n">
+        <v>56.9</v>
+      </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
+      <c r="AB6" t="n">
+        <v>100</v>
+      </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
+      <c r="AF6" t="n">
+        <v>54.5</v>
+      </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -1332,53 +1518,98 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>73.59999999999999</v>
+      </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>254</v>
+      </c>
+      <c r="D7" t="n">
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1391</v>
+      </c>
+      <c r="F7" t="n">
+        <v>69.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>252</v>
+      </c>
+      <c r="H7" t="n">
+        <v>47.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>233</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>433</v>
+      </c>
+      <c r="L7" t="n">
+        <v>21</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>544</v>
+      </c>
+      <c r="N7" t="n">
+        <v>19.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>304</v>
+      </c>
+      <c r="P7" t="n">
+        <v>17.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5178</v>
+      </c>
+      <c r="R7" t="n">
+        <v>55.9</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="T7" t="n">
+        <v>50.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
+      <c r="X7" t="n">
+        <v>47.9</v>
+      </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>330</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>61.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>100</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>48.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>254</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>55.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/ui_runner/templates/graded_analysis_tabs_2026-06-24.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-24.xlsx
@@ -503,13 +503,13 @@
         <v>13</v>
       </c>
       <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
       <c r="G3" t="n">
-        <v>61.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="E4" t="n">
+        <v>191</v>
+      </c>
+      <c r="F4" t="n">
         <v>185</v>
       </c>
-      <c r="F4" t="n">
-        <v>181</v>
-      </c>
       <c r="G4" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="5">
@@ -561,13 +561,13 @@
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -613,16 +613,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="E7" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F7" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G7" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="8">
@@ -645,13 +645,13 @@
         <v>330</v>
       </c>
       <c r="E8" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F8" t="n">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G8" t="n">
-        <v>47.9</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="9">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E10" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F10" t="n">
         <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>73.59999999999999</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="11">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1391</v>
+        <v>1435</v>
       </c>
       <c r="E11" t="n">
-        <v>835</v>
+        <v>861</v>
       </c>
       <c r="F11" t="n">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -758,13 +758,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E12" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="n">
         <v>69.8</v>
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G13" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="E14" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F14" t="n">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="G14" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="15">
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F15" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="16">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G16" t="n">
         <v>19.1</v>
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5178</v>
+        <v>5380</v>
       </c>
       <c r="E17" t="n">
-        <v>926</v>
+        <v>987</v>
       </c>
       <c r="F17" t="n">
-        <v>4252</v>
+        <v>4393</v>
       </c>
       <c r="G17" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
       </c>
     </row>
   </sheetData>
@@ -1519,52 +1519,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="C7" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D7" t="n">
         <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>1391</v>
+        <v>1435</v>
       </c>
       <c r="F7" t="n">
         <v>69.8</v>
       </c>
       <c r="G7" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H7" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="I7" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J7" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="K7" t="n">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="L7" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="M7" t="n">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="N7" t="n">
         <v>19.1</v>
       </c>
       <c r="O7" t="n">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="P7" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>5178</v>
+        <v>5380</v>
       </c>
       <c r="R7" t="n">
         <v>55.9</v>
@@ -1573,37 +1573,37 @@
         <v>34</v>
       </c>
       <c r="T7" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="U7" t="n">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>47.9</v>
+        <v>50.3</v>
       </c>
       <c r="Y7" t="n">
         <v>330</v>
       </c>
       <c r="Z7" t="n">
-        <v>61.5</v>
+        <v>38.5</v>
       </c>
       <c r="AA7" t="n">
         <v>13</v>
       </c>
       <c r="AB7" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="AF7" t="n">
         <v>55.4</v>

--- a/ui_runner/templates/graded_analysis_tabs_2026-06-24.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-24.xlsx
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="E8" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F8" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="G8" t="n">
-        <v>50.3</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="9">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>236</v>
+        <v>294</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F13" t="n">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="14">
@@ -816,16 +816,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>447</v>
+        <v>495</v>
       </c>
       <c r="E14" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F14" t="n">
-        <v>323</v>
+        <v>367</v>
       </c>
       <c r="G14" t="n">
-        <v>27.7</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="15">
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>560</v>
+        <v>790</v>
       </c>
       <c r="E15" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="F15" t="n">
-        <v>440</v>
+        <v>647</v>
       </c>
       <c r="G15" t="n">
-        <v>21.4</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="16">
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5380</v>
+        <v>5210</v>
       </c>
       <c r="E17" t="n">
-        <v>987</v>
+        <v>967</v>
       </c>
       <c r="F17" t="n">
-        <v>4393</v>
+        <v>4243</v>
       </c>
       <c r="G17" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
     </row>
   </sheetData>
@@ -1537,22 +1537,22 @@
         <v>255</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="I7" t="n">
-        <v>236</v>
+        <v>294</v>
       </c>
       <c r="J7" t="n">
-        <v>27.7</v>
+        <v>25.9</v>
       </c>
       <c r="K7" t="n">
-        <v>447</v>
+        <v>495</v>
       </c>
       <c r="L7" t="n">
-        <v>21.4</v>
+        <v>18.1</v>
       </c>
       <c r="M7" t="n">
-        <v>560</v>
+        <v>790</v>
       </c>
       <c r="N7" t="n">
         <v>19.1</v>
@@ -1561,10 +1561,10 @@
         <v>314</v>
       </c>
       <c r="P7" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>5380</v>
+        <v>5210</v>
       </c>
       <c r="R7" t="n">
         <v>55.9</v>
@@ -1582,10 +1582,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.3</v>
+        <v>54.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="Z7" t="n">
         <v>38.5</v>
